--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91355</v>
+        <v>91363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91363</v>
+        <v>91364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B2" t="n">
-        <v>91646</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91646</v>
+        <v>91351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91364</v>
+        <v>91365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B2" t="n">
-        <v>91648</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B3" t="n">
-        <v>91352</v>
+        <v>91648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91648</v>
+        <v>91360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B2" t="n">
-        <v>91656</v>
+        <v>91360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B3" t="n">
-        <v>91360</v>
+        <v>91656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862500</v>
       </c>
       <c r="B2" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862504</v>
       </c>
       <c r="B3" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127862500</v>
+        <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862504</v>
+        <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91748</v>
+        <v>91452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91748</v>
+        <v>91760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127862500</v>
       </c>
       <c r="B3" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127862446</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127862444</v>
       </c>
       <c r="B5" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127862457</v>
       </c>
       <c r="B6" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127862478</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127862502</v>
       </c>
       <c r="B8" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127862504</v>
       </c>
       <c r="B2" t="n">
-        <v>91760</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127862500</v>
+        <v>127862457</v>
       </c>
       <c r="B3" t="n">
-        <v>91464</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405953</v>
+        <v>406014</v>
       </c>
       <c r="R3" t="n">
-        <v>6771564</v>
+        <v>6771491</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127862446</v>
+        <v>127862500</v>
       </c>
       <c r="B4" t="n">
-        <v>91478</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405992</v>
+        <v>405953</v>
       </c>
       <c r="R4" t="n">
-        <v>6771499</v>
+        <v>6771564</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127862444</v>
+        <v>127862446</v>
       </c>
       <c r="B5" t="n">
-        <v>91429</v>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127862457</v>
+        <v>127862502</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406014</v>
+        <v>405953</v>
       </c>
       <c r="R6" t="n">
-        <v>6771491</v>
+        <v>6771564</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127862478</v>
+        <v>127862444</v>
       </c>
       <c r="B7" t="n">
-        <v>91482</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406018</v>
+        <v>405992</v>
       </c>
       <c r="R7" t="n">
-        <v>6771515</v>
+        <v>6771499</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1254,103 +1254,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>127862502</v>
-      </c>
-      <c r="B8" t="n">
-        <v>91918</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Fjällsåskölen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>405953</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6771564</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Malung-Sälen</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Transtrand</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Olov Tranberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20472-2025 artfynd.xlsx
+++ b/artfynd/A 20472-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862457</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862446</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862502</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127862444</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>